--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
   <si>
     <t>Filename</t>
   </si>
@@ -808,694 +808,679 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9976,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.0001,0.0000,0.9988</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.0000,0.0000,0.9997</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8794,0.0580,0.0056,0.0014</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9965,0.0000,0.0000,0.0028</t>
+  </si>
+  <si>
+    <t>0.0023,0.0001,0.0000,0.9995</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0004,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0017,0.9940,0.0005</t>
+  </si>
+  <si>
+    <t>0.1306,0.0012,0.9131,0.0001</t>
+  </si>
+  <si>
+    <t>0.0055,0.0004,0.9934,0.0006</t>
+  </si>
+  <si>
+    <t>0.9888,0.0008,0.0052,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9988,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0576,0.9373,0.0024,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9456,0.0014,0.0459,0.0001</t>
+  </si>
+  <si>
+    <t>0.0222,0.0025,0.9829,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.0002,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0003,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0038,0.0002,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.6207,0.4163,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.7326,0.0789,0.0609,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.9810,0.1094,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9774,0.0003,0.0299,0.0001</t>
+  </si>
+  <si>
+    <t>0.3917,0.6182,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.9980,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.0082,0.0234,0.9589,0.0059</t>
+  </si>
+  <si>
+    <t>0.0024,0.0001,0.9943,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0368,0.0001,0.9561,0.0017</t>
+  </si>
+  <si>
+    <t>0.0001,0.0066,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9990,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0053,0.9958,0.0011</t>
+  </si>
+  <si>
+    <t>0.0006,0.0072,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.0018,0.9977,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9976,0.0473,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0014,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0396,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0029,0.0002,0.9961,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0071,1.0000,0.0021</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9704,0.9871,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9953,0.0023</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9895,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.9977,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9043,0.0022,0.1212,0.0001</t>
+  </si>
+  <si>
+    <t>0.9136,0.0066,0.0571,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0021,0.9996,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9787,0.9910,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9783,0.9655,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9903,0.9810,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.0375,0.9900</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0016,0.9993</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.9940,0.5000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9707,0.9502,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.7374,0.9934,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9937,0.9954,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9906,0.0003,0.0050,0.0000</t>
-  </si>
-  <si>
-    <t>0.4042,0.0005,0.6374,0.0003</t>
-  </si>
-  <si>
-    <t>0.3387,0.0037,0.6168,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0003,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.9764,0.0019,0.0150,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0074,0.9858,0.0031,0.0005</t>
-  </si>
-  <si>
-    <t>0.0007,0.9986,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9731,0.0003,0.0309,0.0001</t>
-  </si>
-  <si>
-    <t>0.0155,0.0002,0.9790,0.0015</t>
-  </si>
-  <si>
-    <t>0.0070,0.0003,0.9927,0.0001</t>
-  </si>
-  <si>
-    <t>0.0797,0.0001,0.9548,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.8587,0.1583,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.7795,0.0135,0.1574,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0074,0.9715,0.0322,0.0009</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9944,0.0009,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.8803,0.1480,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9983,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.0329,0.0739,0.7200,0.0638</t>
-  </si>
-  <si>
-    <t>0.2066,0.0002,0.6873,0.0110</t>
-  </si>
-  <si>
-    <t>0.0007,0.0036,0.9963,0.0006</t>
-  </si>
-  <si>
-    <t>0.0023,0.0002,0.9950,0.0007</t>
-  </si>
-  <si>
-    <t>0.0034,0.0107,0.9948,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.4017,0.0031,0.6216,0.0016</t>
-  </si>
-  <si>
-    <t>0.0032,0.0157,0.0021,0.9864</t>
-  </si>
-  <si>
-    <t>0.0010,0.9973,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9988,0.0327,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0160,0.9948,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.1549,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0017,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
+    <t>0.0002,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0072,0.0003,0.9896,0.0007</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.0002,0.9961,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0052,0.9875,0.0044,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5336,0.5574,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.7846,0.0097,0.1187,0.0025</t>
+  </si>
+  <si>
+    <t>0.5556,0.0022,0.4060,0.0004</t>
+  </si>
+  <si>
+    <t>0.3813,0.0019,0.4968,0.0028</t>
+  </si>
+  <si>
+    <t>0.0044,0.0013,0.9926,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0062,0.0013,0.9968</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9905,0.9971,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9993,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0154,0.9722,0.0093,0.0005</t>
+  </si>
+  <si>
+    <t>0.9722,0.0214,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9908,0.9891,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8485,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0006,0.9988,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0025,0.9999,0.0032</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9923,0.9879,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.0005,0.9934,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0005</t>
-  </si>
-  <si>
-    <t>0.0007,0.9989,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9805,0.0003,0.0279,0.0000</t>
-  </si>
-  <si>
-    <t>0.9608,0.0015,0.0311,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0007,0.9994,0.0025</t>
-  </si>
-  <si>
-    <t>0.0000,0.9466,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9942,0.9773,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9900,0.9948,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0041,0.9991</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0008,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0234,0.9993</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9882,0.7095,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.9956,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9630,0.9873,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9863,0.6855,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9819,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9748,0.9832,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0015,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0682,0.0004,0.9642,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.9900,0.0074,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.9991,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0977,0.9355,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.2098,0.0053,0.7733,0.0014</t>
-  </si>
-  <si>
-    <t>0.0292,0.0005,0.9652,0.0016</t>
-  </si>
-  <si>
-    <t>0.0590,0.0029,0.9276,0.0017</t>
-  </si>
-  <si>
-    <t>0.1391,0.0171,0.8100,0.0014</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.0006,0.9990</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9954,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9981,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0623,0.9271,0.0082,0.0003</t>
-  </si>
-  <si>
-    <t>0.9622,0.0293,0.0032,0.0007</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9752,0.9884,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9788,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0004,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8726,0.0011,0.1035,0.0029</t>
-  </si>
-  <si>
-    <t>0.0075,0.0001,0.9950,0.0001</t>
-  </si>
-  <si>
-    <t>0.9056,0.0063,0.0531,0.0005</t>
-  </si>
-  <si>
-    <t>0.0255,0.0000,0.0000,0.9964</t>
+    <t>0.6255,0.0041,0.3117,0.0012</t>
+  </si>
+  <si>
+    <t>0.0482,0.0002,0.9742,0.0001</t>
+  </si>
+  <si>
+    <t>0.9686,0.0046,0.0063,0.0003</t>
+  </si>
+  <si>
+    <t>0.0151,0.0001,0.0002,0.9957</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0046,0.9987</t>
-  </si>
-  <si>
-    <t>0.0003,0.9261,0.9656,0.0001</t>
-  </si>
-  <si>
-    <t>0.4605,0.5873,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0241,0.9689,0.0048,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.6863,0.0007,0.0000,0.3319</t>
+    <t>0.0000,0.0000,0.0003,0.9999</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.0378,0.9930</t>
+  </si>
+  <si>
+    <t>0.0000,0.9899,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0114,0.9847,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0925,0.8817,0.0017,0.0016</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.5279,0.0006,0.0030,0.6305</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0004,0.0267,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.9572,0.0000,0.0165,0.0047</t>
-  </si>
-  <si>
-    <t>0.9974,0.0000,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.8520,0.0765,0.0143,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.7071,0.0947,0.0277,0.0006</t>
-  </si>
-  <si>
-    <t>0.9825,0.0021,0.0077,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0003,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9959,0.0008,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.8397,0.2944,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7569,0.1564,0.0234,0.0012</t>
-  </si>
-  <si>
-    <t>0.1791,0.8018,0.0169,0.0006</t>
-  </si>
-  <si>
-    <t>0.0310,0.1448,0.9635,0.0009</t>
-  </si>
-  <si>
-    <t>0.8660,0.2617,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9725,0.0209,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.0498,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9830,0.0056,0.0054,0.0026</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0634,0.9894,0.0005</t>
-  </si>
-  <si>
-    <t>0.0019,0.0014,0.9976,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0030,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.0034,0.9873,0.0030</t>
-  </si>
-  <si>
-    <t>0.0970,0.0004,0.9393,0.0001</t>
-  </si>
-  <si>
-    <t>0.4363,0.0103,0.4215,0.0004</t>
-  </si>
-  <si>
-    <t>0.0203,0.0018,0.9760,0.0004</t>
-  </si>
-  <si>
-    <t>0.0137,0.9592,0.0281,0.0007</t>
-  </si>
-  <si>
-    <t>0.0058,0.0049,0.9887,0.0002</t>
-  </si>
-  <si>
-    <t>0.6484,0.0053,0.2311,0.0032</t>
-  </si>
-  <si>
-    <t>0.1273,0.0028,0.8444,0.0025</t>
-  </si>
-  <si>
-    <t>0.0025,0.9954,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.9985,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.5708,0.4977,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.5719,0.5333,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.6801,0.4569,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9548,0.0039,0.0183,0.0002</t>
-  </si>
-  <si>
-    <t>0.9625,0.0003,0.0550,0.0000</t>
-  </si>
-  <si>
-    <t>0.9872,0.0005,0.0033,0.0007</t>
-  </si>
-  <si>
-    <t>0.4830,0.0011,0.6493,0.0000</t>
-  </si>
-  <si>
-    <t>0.1770,0.0002,0.8789,0.0003</t>
-  </si>
-  <si>
-    <t>0.0046,0.0002,0.9960,0.0003</t>
-  </si>
-  <si>
-    <t>0.0019,0.0027,0.9938,0.0007</t>
-  </si>
-  <si>
-    <t>0.0043,0.0080,0.9911,0.0002</t>
-  </si>
-  <si>
-    <t>0.0031,0.0009,0.9946,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.0065,0.9875,0.0011</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0006,0.0001,0.0002</t>
+    <t>0.0014,0.0371,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.9943,0.0000,0.0014,0.0021</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.8364,0.2161,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0010,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.1110,0.5797,0.0632,0.0014</t>
+  </si>
+  <si>
+    <t>0.9887,0.0025,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8786,0.0920,0.0114,0.0009</t>
+  </si>
+  <si>
+    <t>0.3160,0.7203,0.0064,0.0004</t>
+  </si>
+  <si>
+    <t>0.1783,0.0896,0.7835,0.0004</t>
+  </si>
+  <si>
+    <t>0.8559,0.2884,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9832,0.0073,0.0030,0.0022</t>
+  </si>
+  <si>
+    <t>0.0000,0.0080,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9615,0.0069,0.0207,0.0018</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0801,0.0039,0.9164,0.0016</t>
+  </si>
+  <si>
+    <t>0.0200,0.0015,0.9871,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0033,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0337,0.0029,0.9445,0.0041</t>
+  </si>
+  <si>
+    <t>0.0695,0.0012,0.9467,0.0003</t>
+  </si>
+  <si>
+    <t>0.0068,0.0014,0.9878,0.0010</t>
+  </si>
+  <si>
+    <t>0.0081,0.0021,0.9900,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.6338,0.7950,0.0004</t>
+  </si>
+  <si>
+    <t>0.0041,0.0025,0.9921,0.0001</t>
+  </si>
+  <si>
+    <t>0.9643,0.0039,0.0071,0.0009</t>
+  </si>
+  <si>
+    <t>0.5256,0.0046,0.3554,0.0033</t>
+  </si>
+  <si>
+    <t>0.0133,0.9845,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.1430,0.8726,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.4530,0.6771,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.4254,0.6999,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9907,0.0015,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.9214,0.0005,0.0945,0.0001</t>
+  </si>
+  <si>
+    <t>0.9798,0.0007,0.0065,0.0007</t>
+  </si>
+  <si>
+    <t>0.2624,0.0024,0.7881,0.0002</t>
+  </si>
+  <si>
+    <t>0.0985,0.0009,0.9196,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0219,0.0408,0.9335,0.0020</t>
+  </si>
+  <si>
+    <t>0.0008,0.0016,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.0004,0.9950,0.0002</t>
+  </si>
+  <si>
+    <t>0.0148,0.0245,0.9251,0.0019</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9988,0.0012</t>
+  </si>
+  <si>
+    <t>0.0062,0.1992,0.9211,0.0011</t>
+  </si>
+  <si>
+    <t>0.8835,0.0004,0.0950,0.0027</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.6580,0.9714,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0019,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0938,0.0005,0.8957,0.0026</t>
+  </si>
+  <si>
+    <t>0.9823,0.0017,0.0063,0.0000</t>
+  </si>
+  <si>
+    <t>0.3186,0.0004,0.7570,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0014,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9987,0.0009,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9974,0.0022,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0100,0.9991,0.0009</t>
-  </si>
-  <si>
-    <t>0.0110,0.5226,0.4680,0.0013</t>
-  </si>
-  <si>
-    <t>0.9782,0.0003,0.0157,0.0009</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.4497,0.9316,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0006,0.9937,0.0005</t>
-  </si>
-  <si>
-    <t>0.6463,0.0003,0.3723,0.0010</t>
-  </si>
-  <si>
-    <t>0.8664,0.0039,0.1039,0.0004</t>
-  </si>
-  <si>
-    <t>0.6009,0.0001,0.5790,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0001,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0048,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0025,0.0017,0.9943,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0022,0.9983,0.0003</t>
-  </si>
-  <si>
-    <t>0.0047,0.0033,0.9912,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.3134,0.0006,0.4886,0.0373</t>
-  </si>
-  <si>
-    <t>0.0249,0.0004,0.9787,0.0005</t>
-  </si>
-  <si>
-    <t>0.0021,0.0001,0.9940,0.0015</t>
-  </si>
-  <si>
-    <t>0.7649,0.0000,0.0005,0.3990</t>
-  </si>
-  <si>
-    <t>0.0010,0.0025,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0213,0.0003,0.0000,0.9955</t>
-  </si>
-  <si>
-    <t>0.9513,0.0004,0.0001,0.0460</t>
+    <t>0.9990,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.0007,0.9935,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0031,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0026,0.9951,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.0066,0.9944,0.0005</t>
+  </si>
+  <si>
+    <t>0.0060,0.0000,0.9953,0.0001</t>
+  </si>
+  <si>
+    <t>0.4388,0.0001,0.1388,0.0554</t>
+  </si>
+  <si>
+    <t>0.0069,0.0004,0.9930,0.0004</t>
+  </si>
+  <si>
+    <t>0.0050,0.0001,0.9893,0.0022</t>
+  </si>
+  <si>
+    <t>0.9951,0.0001,0.0003,0.0030</t>
+  </si>
+  <si>
+    <t>0.0082,0.0005,0.0001,0.9980</t>
+  </si>
+  <si>
+    <t>0.0490,0.0003,0.0001,0.9888</t>
+  </si>
+  <si>
+    <t>0.9821,0.0006,0.0001,0.0086</t>
   </si>
 </sst>
 </file>
@@ -1881,7 +1866,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1895,7 +1880,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1909,7 +1894,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1923,7 +1908,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1937,7 +1922,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1951,7 +1936,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1965,7 +1950,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1979,7 +1964,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1993,7 +1978,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2007,7 +1992,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2021,7 +2006,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2035,7 +2020,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2049,7 +2034,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2063,7 +2048,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2077,7 +2062,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2091,7 +2076,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2105,7 +2090,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2119,7 +2104,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2133,7 +2118,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2147,7 +2132,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2161,7 +2146,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2175,7 +2160,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2189,7 +2174,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2200,10 +2185,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2217,7 +2202,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2231,7 +2216,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2245,7 +2230,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2259,7 +2244,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2273,7 +2258,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2287,7 +2272,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2301,7 +2286,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2315,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2329,7 +2314,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2343,7 +2328,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2357,7 +2342,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2368,10 +2353,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2385,7 +2370,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2399,7 +2384,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2413,7 +2398,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2427,7 +2412,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2441,7 +2426,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2455,7 +2440,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2469,7 +2454,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2483,7 +2468,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2497,7 +2482,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2511,7 +2496,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2525,7 +2510,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2539,7 +2524,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2553,7 +2538,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2567,7 +2552,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2581,7 +2566,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2595,7 +2580,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2609,7 +2594,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2623,7 +2608,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2637,7 +2622,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2651,7 +2636,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2665,7 +2650,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2679,7 +2664,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2693,7 +2678,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2707,7 +2692,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2721,7 +2706,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2735,7 +2720,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2749,7 +2734,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2763,7 +2748,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2777,7 +2762,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2791,7 +2776,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2805,7 +2790,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2819,7 +2804,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2833,7 +2818,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2847,7 +2832,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2861,7 +2846,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2875,7 +2860,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2889,7 +2874,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2903,7 +2888,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2917,7 +2902,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2931,7 +2916,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2945,7 +2930,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2959,7 +2944,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2973,7 +2958,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2987,7 +2972,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3001,7 +2986,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3012,10 +2997,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3029,7 +3014,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3043,7 +3028,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3057,7 +3042,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3071,7 +3056,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3085,7 +3070,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3099,7 +3084,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3113,7 +3098,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3127,7 +3112,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3141,7 +3126,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3155,7 +3140,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3169,7 +3154,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>275</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3183,7 +3168,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3197,7 +3182,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3211,7 +3196,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>353</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3225,7 +3210,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3239,7 +3224,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3253,7 +3238,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>316</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3267,7 +3252,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>355</v>
+        <v>274</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3281,7 +3266,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>268</v>
+        <v>356</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3295,7 +3280,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>315</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3309,7 +3294,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3323,7 +3308,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3337,7 +3322,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3351,7 +3336,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3365,7 +3350,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3379,7 +3364,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3393,7 +3378,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3407,7 +3392,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3421,7 +3406,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3435,7 +3420,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>278</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3449,7 +3434,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>278</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3460,10 +3445,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3474,10 +3459,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3488,10 +3473,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3502,10 +3487,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3519,7 +3504,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3533,7 +3518,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3547,7 +3532,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3561,7 +3546,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3575,7 +3560,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3589,7 +3574,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3603,7 +3588,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3617,7 +3602,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3631,7 +3616,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3645,7 +3630,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3659,7 +3644,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3673,7 +3658,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>316</v>
+        <v>271</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3687,7 +3672,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3701,7 +3686,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3715,7 +3700,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3729,7 +3714,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3743,7 +3728,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>271</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3939,7 +3924,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>353</v>
+        <v>271</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4006,7 +3991,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D154" t="s">
         <v>399</v>
@@ -4118,7 +4103,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>407</v>
@@ -4177,7 +4162,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>411</v>
+        <v>322</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4191,7 +4176,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4205,7 +4190,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4219,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4247,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>269</v>
+        <v>322</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4261,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4275,7 +4260,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4289,7 +4274,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4303,7 +4288,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4317,7 +4302,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4331,7 +4316,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4345,7 +4330,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4359,7 +4344,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4373,7 +4358,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4387,7 +4372,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4401,7 +4386,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4415,7 +4400,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4429,7 +4414,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4443,7 +4428,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4457,7 +4442,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4471,7 +4456,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4485,7 +4470,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4499,7 +4484,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4513,7 +4498,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4527,7 +4512,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4538,10 +4523,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4555,7 +4540,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4566,10 +4551,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D194" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4583,7 +4568,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4597,7 +4582,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4608,10 +4593,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4625,7 +4610,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4639,7 +4624,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4650,10 +4635,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4667,7 +4652,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4678,10 +4663,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4695,7 +4680,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4709,7 +4694,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4723,7 +4708,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4737,7 +4722,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4751,7 +4736,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4765,7 +4750,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4779,7 +4764,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4793,7 +4778,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4807,7 +4792,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4821,7 +4806,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4835,7 +4820,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4849,7 +4834,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>455</v>
+        <v>323</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4877,7 +4862,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>457</v>
+        <v>323</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4891,7 +4876,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4905,7 +4890,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>352</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4919,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>459</v>
+        <v>323</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4933,7 +4918,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>269</v>
+        <v>357</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4947,7 +4932,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4958,10 +4943,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4975,7 +4960,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4989,7 +4974,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>463</v>
+        <v>292</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5003,7 +4988,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5014,10 +4999,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5031,7 +5016,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5045,7 +5030,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5059,7 +5044,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5073,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5084,10 +5069,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5101,7 +5086,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5115,7 +5100,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5129,7 +5114,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5143,7 +5128,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5157,7 +5142,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5171,7 +5156,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>476</v>
+        <v>323</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5185,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5199,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>478</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5213,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5227,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5241,7 +5226,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>481</v>
+        <v>323</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5255,7 +5240,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5269,7 +5254,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5283,7 +5268,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5297,7 +5282,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5311,7 +5296,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5322,10 +5307,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5339,7 +5324,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5353,7 +5338,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5367,7 +5352,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5381,7 +5366,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5395,7 +5380,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5437,7 +5422,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
